--- a/assets/docs/lop4/Dao duc - Lop 4.xlsx
+++ b/assets/docs/lop4/Dao duc - Lop 4.xlsx
@@ -825,7 +825,8 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở bài “Yêu lao động”, GV chiếu bộ ảnh người lao động ở nhiều nghề.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài “Yêu lao động”, GV chiếu bộ ảnh người lao động ở nhiều nghề và ảnh HS làm việc vừa sức như trực nhật, tưới cây, gấp quần áo
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV gõ lên màn hình những việc HS kể thành bảng hai cột việc ở nhà và việc ở trường; cả lớp cùng đọc
 KNS: KN chi tiêu và giữ gìn: dùng đồ dùng, tiền bạc hợp lí, giữ gìn của công.</t>
         </is>
       </c>

--- a/assets/docs/lop4/Dao duc - Lop 4.xlsx
+++ b/assets/docs/lop4/Dao duc - Lop 4.xlsx
@@ -1032,11 +1032,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>NLS-GT (Cơ bản 2): HS cùng xây dựng bản quy ước sử dụng phòng máy và bảng phân công trực nhật, mỗi tổ theo dõi và.</t>
-        </is>
-      </c>
+      <c r="H20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1319,11 +1315,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Cho HS quan sát các cách tiêu tiền trên môi trường số: mua hàng qua mạng, nạp tiền vào trò chơi, mua.</t>
-        </is>
-      </c>
+      <c r="H29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
